--- a/data/trending_integrated_20261029_09.xlsx
+++ b/data/trending_integrated_20261029_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>545000</v>
+        <v>15120</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.06%</t>
+          <t>'+5.07%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>297</v>
+        <v>161</v>
       </c>
       <c r="H2" t="n">
-        <v>24.78</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>534000</v>
+        <v>14390</v>
       </c>
       <c r="K2" t="n">
-        <v>546000</v>
+        <v>15450</v>
       </c>
       <c r="L2" t="n">
-        <v>563000</v>
+        <v>16290</v>
       </c>
       <c r="M2" t="n">
-        <v>538000</v>
+        <v>15070</v>
       </c>
       <c r="N2" t="n">
-        <v>24.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>80737511000</v>
+        <v>21411905550</v>
       </c>
       <c r="P2" t="n">
-        <v>723000</v>
+        <v>49800</v>
       </c>
       <c r="Q2" t="n">
-        <v>259000</v>
+        <v>8180</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성SDI, 26년 3분기 영업이익 컨센서스 상회 및 실적 호조. 전고체 관련주 급등 및 금리 동결 영향 언급.</t>
+          <t>의료 AI 섹터 강세 및 템퍼스AI 급등에 따른 동반 상승 기대. 3분기 실적 발표 전까지 보유 관점 유지.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['영업이익', '컨센서스', '전고체']</t>
+          <t>['의료AI', '실적발표', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1517000</v>
+        <v>1539000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+3.50%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>468</v>
       </c>
       <c r="G3" t="n">
-        <v>2162</v>
+        <v>1869</v>
       </c>
       <c r="H3" t="n">
         <v>48.66</v>
@@ -693,7 +693,7 @@
         <v>1511000</v>
       </c>
       <c r="L3" t="n">
-        <v>1520000</v>
+        <v>1547000</v>
       </c>
       <c r="M3" t="n">
         <v>1501000</v>
@@ -702,7 +702,7 @@
         <v>48.61</v>
       </c>
       <c r="O3" t="n">
-        <v>320407477500</v>
+        <v>756702610500</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SK하이닉스, 구글 실적 부진 속에서도 ADR 13% 상승. 자사주 매입 신청 및 '어닝콜' 슈퍼사이클 연장 전망 언급.</t>
+          <t>자사주 매입 기대와 함께 160, 170 탈환 및 200 돌파 전망. 구글 악재에도 불구하고 반도체 급등 분위기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['ADR', '자사주 매입', '슈퍼사이클']</t>
+          <t>['자사주매입', '반도체', '낙폭']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,60 +747,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>240250</v>
+        <v>19710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.72%</t>
+          <t>'+2.60%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>-0.46</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>466</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>2214</v>
+        <v>53</v>
       </c>
       <c r="H4" t="n">
-        <v>46.19</v>
+        <v>0.65</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>242000</v>
+        <v>19210</v>
       </c>
       <c r="K4" t="n">
-        <v>241000</v>
+        <v>19010</v>
       </c>
       <c r="L4" t="n">
-        <v>241000</v>
+        <v>19830</v>
       </c>
       <c r="M4" t="n">
-        <v>239000</v>
+        <v>18620</v>
       </c>
       <c r="N4" t="n">
-        <v>46.15</v>
+        <v>1.11</v>
       </c>
       <c r="O4" t="n">
-        <v>176823287500</v>
+        <v>30902170970</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>94500</v>
+        <v>11550</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자, 컨퍼런스 콜 앞두고 주주환원 정책 기대감 및 마이크론 주가 급등 소식. 파운드리 흑자 전환 소식은 일부 언급.</t>
+          <t>급락 및 거래량 증가 속에서 허매도 의혹 제기. 단기 상승 후 조정 가능성 및 개인 투자자 손실 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,20 +819,388 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['컨퍼런스 콜', '주주환원', '파운드리']</t>
+          <t>['급락', '거래량', '허매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>244000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+0.83%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>465</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2057</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>242000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>244500</v>
+      </c>
+      <c r="M5" t="n">
+        <v>239000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>422954307250</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>정치적 논쟁 속에서 긍정적 전망과 함께 컨퍼런스콜 및 주주환원 정책 발표 기대. 파운드리 흑자 소식 확인.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['컨퍼런스콜', '주주환원', '파운드리']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
         <v>20</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15030</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+0.33%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" t="n">
+        <v>317</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>14980</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15120</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15260</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14650</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20717173545</v>
+      </c>
+      <c r="P6" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1819</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>메타 관련 뉴스 및 미국장 상승에 따른 광통신주 급등 기대. 루멘텀 인수설 및 연말 3만 목표 제시.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['메타', '광통신', '루멘텀']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>533000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-0.19%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>109</v>
+      </c>
+      <c r="F7" t="n">
+        <v>76</v>
+      </c>
+      <c r="G7" t="n">
+        <v>396</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>534000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>546000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>563000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>524000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>144903569500</v>
+      </c>
+      <c r="P7" t="n">
+        <v>723000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>259000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>컨퍼런스콜 통한 대규모 주주환원 정책 발표 기대감 속에서 4분기 실적 어닝 서프라이즈 전망. ESS 및 전고체 관련주 강세.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['컨퍼런스콜', '어닝서프라이즈', '주주환원']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13770</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-3.50%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>145</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13750</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7002400190</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>대차 해지 독려에도 불구하고 지속적인 하락 및 목표가 하향 공시. 공매도 세력 활동 의혹 제기.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['공매도', '목표가하향', '대차해지']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>047040</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261029_09.xlsx
+++ b/data/trending_integrated_20261029_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15120</v>
+        <v>15020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+5.07%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
         <v>8.050000000000001</v>
@@ -604,13 +604,13 @@
         <v>16290</v>
       </c>
       <c r="M2" t="n">
-        <v>15070</v>
+        <v>14800</v>
       </c>
       <c r="N2" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>21411905550</v>
+        <v>25417249610</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -619,23 +619,23 @@
         <v>8180</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-168000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 강세 및 템퍼스AI 급등에 따른 동반 상승 기대. 3분기 실적 발표 전까지 보유 관점 유지.</t>
+          <t>루닛, 의료 AI 분야 대장주로 미국 시장 급등. 공매도 세력과의 싸움 및 3분기 실적 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['의료AI', '실적발표', '숏스퀴즈']</t>
+          <t>['의료AI', '공매도', '실적']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1539000</v>
+        <v>1550000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.50%</t>
+          <t>'+4.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G3" t="n">
-        <v>1869</v>
+        <v>1701</v>
       </c>
       <c r="H3" t="n">
         <v>48.66</v>
@@ -693,7 +693,7 @@
         <v>1511000</v>
       </c>
       <c r="L3" t="n">
-        <v>1547000</v>
+        <v>1555000</v>
       </c>
       <c r="M3" t="n">
         <v>1501000</v>
@@ -702,7 +702,7 @@
         <v>48.61</v>
       </c>
       <c r="O3" t="n">
-        <v>756702610500</v>
+        <v>1015023192000</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -711,23 +711,23 @@
         <v>501000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>146000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자사주 매입 기대와 함께 160, 170 탈환 및 200 돌파 전망. 구글 악재에도 불구하고 반도체 급등 분위기.</t>
+          <t>SK하이닉스, 구글 주가 급락 속에서 대장주 역할 기대. 기술적 반등 및 300만원 목표 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주매입', '반도체', '낙폭']</t>
+          <t>['대장주', '기술적반등', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19710</v>
+        <v>15570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.60%</t>
+          <t>'+3.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.46</v>
+        <v>0.46</v>
       </c>
       <c r="E4" t="n">
         <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>53</v>
+        <v>373</v>
       </c>
       <c r="H4" t="n">
-        <v>0.65</v>
+        <v>3.33</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19210</v>
+        <v>14980</v>
       </c>
       <c r="K4" t="n">
-        <v>19010</v>
+        <v>15120</v>
       </c>
       <c r="L4" t="n">
-        <v>19830</v>
+        <v>15640</v>
       </c>
       <c r="M4" t="n">
-        <v>18620</v>
+        <v>14650</v>
       </c>
       <c r="N4" t="n">
-        <v>1.11</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>30902170970</v>
+        <v>44106242905</v>
       </c>
       <c r="P4" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>11550</v>
+        <v>1819</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급락 및 거래량 증가 속에서 허매도 의혹 제기. 단기 상승 후 조정 가능성 및 개인 투자자 손실 우려.</t>
+          <t>대한광통신, 메타 관련 뉴스 및 삼성전자 인수 기대감. 미국 시장 호조 및 3만원 목표.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['급락', '거래량', '허매도']</t>
+          <t>['메타', '인수', '미국장']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>244000</v>
+        <v>547000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.83%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>465</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>2057</v>
+        <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>46.19</v>
+        <v>24.78</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>242000</v>
+        <v>534000</v>
       </c>
       <c r="K5" t="n">
-        <v>241000</v>
+        <v>546000</v>
       </c>
       <c r="L5" t="n">
-        <v>244500</v>
+        <v>563000</v>
       </c>
       <c r="M5" t="n">
-        <v>239000</v>
+        <v>524000</v>
       </c>
       <c r="N5" t="n">
-        <v>46.15</v>
+        <v>24.86</v>
       </c>
       <c r="O5" t="n">
-        <v>422954307250</v>
+        <v>184328666500</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>723000</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>259000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 논쟁 속에서 긍정적 전망과 함께 컨퍼런스콜 및 주주환원 정책 발표 기대. 파운드리 흑자 소식 확인.</t>
+          <t>삼성SDI, 26년 3분기 영업이익 컨센서스 상회 및 어닝 서프라이즈. ESS, 전고체 관련주 급등.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '주주환원', '파운드리']</t>
+          <t>['어닝서프라이즈', 'ESS', '전고체']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15030</v>
+        <v>245250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>462</v>
       </c>
       <c r="G6" t="n">
-        <v>317</v>
+        <v>1793</v>
       </c>
       <c r="H6" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14980</v>
+        <v>242000</v>
       </c>
       <c r="K6" t="n">
-        <v>15120</v>
+        <v>241000</v>
       </c>
       <c r="L6" t="n">
-        <v>15260</v>
+        <v>246000</v>
       </c>
       <c r="M6" t="n">
-        <v>14650</v>
+        <v>239000</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>46.15</v>
       </c>
       <c r="O6" t="n">
-        <v>20717173545</v>
+        <v>624629250250</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1819</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>메타 관련 뉴스 및 미국장 상승에 따른 광통신주 급등 기대. 루멘텀 인수설 및 연말 3만 목표 제시.</t>
+          <t>삼성전자, 파운드리 흑자 및 구글 투자 확대 뉴스. 성과급 논란과 주주환원 정책 발표 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['메타', '광통신', '루멘텀']</t>
+          <t>['파운드리', '주주환원', '투자']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>533000</v>
+        <v>18770</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>-0.46</v>
       </c>
       <c r="E7" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>396</v>
+        <v>63</v>
       </c>
       <c r="H7" t="n">
-        <v>24.78</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>534000</v>
+        <v>19210</v>
       </c>
       <c r="K7" t="n">
-        <v>546000</v>
+        <v>19010</v>
       </c>
       <c r="L7" t="n">
-        <v>563000</v>
+        <v>19840</v>
       </c>
       <c r="M7" t="n">
-        <v>524000</v>
+        <v>18440</v>
       </c>
       <c r="N7" t="n">
-        <v>24.86</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>144903569500</v>
+        <v>44218108915</v>
       </c>
       <c r="P7" t="n">
-        <v>723000</v>
+        <v>28800</v>
       </c>
       <c r="Q7" t="n">
-        <v>259000</v>
+        <v>11550</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 통한 대규모 주주환원 정책 발표 기대감 속에서 4분기 실적 어닝 서프라이즈 전망. ESS 및 전고체 관련주 강세.</t>
+          <t>멜콘, 반도체 대폭락 및 주가 하락 불가피 언급. 시초 하락 및 개인 투자자 손실 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '어닝서프라이즈', '주주환원']</t>
+          <t>['반도체', '폭락', '하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13770</v>
+        <v>13680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
         <v>9.6</v>
@@ -1156,13 +1156,13 @@
         <v>14180</v>
       </c>
       <c r="M8" t="n">
-        <v>13750</v>
+        <v>13670</v>
       </c>
       <c r="N8" t="n">
         <v>9.83</v>
       </c>
       <c r="O8" t="n">
-        <v>7002400190</v>
+        <v>11823918175</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1171,14 +1171,14 @@
         <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대차 해지 독려에도 불구하고 지속적인 하락 및 목표가 하향 공시. 공매도 세력 활동 의혹 제기.</t>
+          <t>대우건설, 목표가 하향 및 공매도 관련 부정적 언급. 주가 하락 및 외인 비중 변동.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '목표가하향', '대차해지']</t>
+          <t>['공매도', '목표가', '외인비중']</t>
         </is>
       </c>
       <c r="X8" t="n">

--- a/data/trending_integrated_20261029_09.xlsx
+++ b/data/trending_integrated_20261029_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15020</v>
+        <v>8610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.06</v>
+        <v>-1.04</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
-        <v>8.050000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>14390</v>
+        <v>7450</v>
       </c>
       <c r="K2" t="n">
-        <v>15450</v>
+        <v>7470</v>
       </c>
       <c r="L2" t="n">
-        <v>16290</v>
+        <v>9680</v>
       </c>
       <c r="M2" t="n">
-        <v>14800</v>
+        <v>7360</v>
       </c>
       <c r="N2" t="n">
-        <v>8.109999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="O2" t="n">
-        <v>25417249610</v>
+        <v>62461511285</v>
       </c>
       <c r="P2" t="n">
-        <v>49800</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>8180</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>-168000</v>
+        <v>144000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>루닛, 의료 AI 분야 대장주로 미국 시장 급등. 공매도 세력과의 싸움 및 3분기 실적 기대.</t>
+          <t>광주 반도체 공장 관련 뉴스와 함께 프로그램 매집 정황이 포착되며 주가 상승에 대한 기대감이 나타나고 있으나, 일부에서는 주가 조작에 대한 우려도 제기된다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도', '실적']</t>
+          <t>['광주 반도체', '프로그램 매집', '주가 조작']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1550000</v>
+        <v>15910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.24%</t>
+          <t>'+6.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>0.46</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>465</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>1701</v>
+        <v>428</v>
       </c>
       <c r="H3" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1487000</v>
+        <v>14980</v>
       </c>
       <c r="K3" t="n">
-        <v>1511000</v>
+        <v>15120</v>
       </c>
       <c r="L3" t="n">
-        <v>1555000</v>
+        <v>15950</v>
       </c>
       <c r="M3" t="n">
-        <v>1501000</v>
+        <v>14650</v>
       </c>
       <c r="N3" t="n">
-        <v>48.61</v>
+        <v>2.87</v>
       </c>
       <c r="O3" t="n">
-        <v>1015023192000</v>
+        <v>66051352465</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q3" t="n">
-        <v>501000</v>
+        <v>1819</v>
       </c>
       <c r="R3" t="n">
-        <v>146000</v>
+        <v>-102000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SK하이닉스, 구글 주가 급락 속에서 대장주 역할 기대. 기술적 반등 및 300만원 목표 언급.</t>
+          <t>미국장 및 광통신 섹터의 강세와 루멘텀 인수 기대감으로 주가 급등 가능성이 제기되고 있으며, 연말 3만 원 돌파 전망과 함께 계약 공시 기대감이 존재한다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['대장주', '기술적반등', '목표가']</t>
+          <t>['광통신', '루멘텀 인수', '계약 공시']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15570</v>
+        <v>1567000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.94%</t>
+          <t>'+5.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>467</v>
       </c>
       <c r="G4" t="n">
-        <v>373</v>
+        <v>1721</v>
       </c>
       <c r="H4" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14980</v>
+        <v>1487000</v>
       </c>
       <c r="K4" t="n">
-        <v>15120</v>
+        <v>1511000</v>
       </c>
       <c r="L4" t="n">
-        <v>15640</v>
+        <v>1576000</v>
       </c>
       <c r="M4" t="n">
-        <v>14650</v>
+        <v>1501000</v>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>48.61</v>
       </c>
       <c r="O4" t="n">
-        <v>44106242905</v>
+        <v>1365453789500</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1819</v>
+        <v>501000</v>
       </c>
       <c r="R4" t="n">
-        <v>-102000</v>
+        <v>146000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대한광통신, 메타 관련 뉴스 및 삼성전자 인수 기대감. 미국 시장 호조 및 3만원 목표.</t>
+          <t>SK하이닉스의 향후 주가 상승 전망이 강하게 제기되고 있으며, 자사주 매입 발표에 대한 기대감이 존재한다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['메타', '인수', '미국장']</t>
+          <t>['SK하이닉스', '자사주 매입', '주가 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>547000</v>
+        <v>4420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+5.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>460</v>
+        <v>118</v>
       </c>
       <c r="H5" t="n">
-        <v>24.78</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>534000</v>
+        <v>4195</v>
       </c>
       <c r="K5" t="n">
-        <v>546000</v>
+        <v>4280</v>
       </c>
       <c r="L5" t="n">
-        <v>563000</v>
+        <v>4480</v>
       </c>
       <c r="M5" t="n">
-        <v>524000</v>
+        <v>4100</v>
       </c>
       <c r="N5" t="n">
-        <v>24.86</v>
+        <v>1.2</v>
       </c>
       <c r="O5" t="n">
-        <v>184328666500</v>
+        <v>101146534737</v>
       </c>
       <c r="P5" t="n">
-        <v>723000</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>259000</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>12000</v>
+        <v>238000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성SDI, 26년 3분기 영업이익 컨센서스 상회 및 어닝 서프라이즈. ESS, 전고체 관련주 급등.</t>
+          <t>글로벌 광통신 섹터의 강세와 루멘텀의 폭등 소식에 힘입어 주가 상승 기대감이 고조되고 있으며, 5G 상용화 및 글로벌 기업 공급 시작과 관련된 긍정적인 뉴스가 존재한다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', 'ESS', '전고체']</t>
+          <t>['광통신', '루멘텀', '5G 상용화']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>245250</v>
+        <v>551000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.34%</t>
+          <t>'+3.18%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>149</v>
       </c>
       <c r="F6" t="n">
-        <v>462</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
-        <v>1793</v>
+        <v>539</v>
       </c>
       <c r="H6" t="n">
-        <v>46.19</v>
+        <v>24.78</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>242000</v>
+        <v>534000</v>
       </c>
       <c r="K6" t="n">
-        <v>241000</v>
+        <v>546000</v>
       </c>
       <c r="L6" t="n">
-        <v>246000</v>
+        <v>563000</v>
       </c>
       <c r="M6" t="n">
-        <v>239000</v>
+        <v>524000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.15</v>
+        <v>24.86</v>
       </c>
       <c r="O6" t="n">
-        <v>624629250250</v>
+        <v>217950208500</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>723000</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>259000</v>
       </c>
       <c r="R6" t="n">
-        <v>258000</v>
+        <v>12000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자, 파운드리 흑자 및 구글 투자 확대 뉴스. 성과급 논란과 주주환원 정책 발표 기대.</t>
+          <t>컨퍼런스 콜에서 발표된 26년 3분기 영업이익이 컨센서스를 상회했으며, 실적 호조에 따른 주가 상승 기대감이 존재한다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['파운드리', '주주환원', '투자']</t>
+          <t>['컨퍼런스 콜', '실적', '어닝 서프라이즈']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18770</v>
+        <v>245750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'+1.55%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>463</v>
       </c>
       <c r="G7" t="n">
-        <v>63</v>
+        <v>1601</v>
       </c>
       <c r="H7" t="n">
-        <v>0.65</v>
+        <v>46.19</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19210</v>
+        <v>242000</v>
       </c>
       <c r="K7" t="n">
-        <v>19010</v>
+        <v>241000</v>
       </c>
       <c r="L7" t="n">
-        <v>19840</v>
+        <v>247500</v>
       </c>
       <c r="M7" t="n">
-        <v>18440</v>
+        <v>239000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>46.15</v>
       </c>
       <c r="O7" t="n">
-        <v>44218108915</v>
+        <v>898744423500</v>
       </c>
       <c r="P7" t="n">
-        <v>28800</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>11550</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>53000</v>
+        <v>258000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>멜콘, 반도체 대폭락 및 주가 하락 불가피 언급. 시초 하락 및 개인 투자자 손실 우려.</t>
+          <t>컨퍼런스 콜에서의 주주환원 정책 발표 기대감과 성과급 관련 논란이 혼재되어 있으며, 외인 매수세와 기관 매도세가 엇갈리고 있다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '폭락', '하락']</t>
+          <t>['컨퍼런스 콜', '주주환원', '성과급']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13680</v>
+        <v>14460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H8" t="n">
-        <v>9.6</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14270</v>
+        <v>14390</v>
       </c>
       <c r="K8" t="n">
-        <v>14180</v>
+        <v>15450</v>
       </c>
       <c r="L8" t="n">
-        <v>14180</v>
+        <v>16290</v>
       </c>
       <c r="M8" t="n">
-        <v>13670</v>
+        <v>14430</v>
       </c>
       <c r="N8" t="n">
-        <v>9.83</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>11823918175</v>
+        <v>28631924740</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>31000</v>
+        <v>-168000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대우건설, 목표가 하향 및 공매도 관련 부정적 언급. 주가 하락 및 외인 비중 변동.</t>
+          <t>미국 의료 AI 섹터 급등 및 ESMO 2026 스코프에 대한 기대감. 3분기 실적 발표까지 보유 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,18 +1187,386 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '목표가', '외인비중']</t>
+          <t>['의료 AI', 'ESMO 2026', '실적 발표']</t>
         </is>
       </c>
       <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>62900</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.02%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>37</v>
+      </c>
+      <c r="G9" t="n">
+        <v>262</v>
+      </c>
+      <c r="H9" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>64200</v>
+      </c>
+      <c r="K9" t="n">
+        <v>64200</v>
+      </c>
+      <c r="L9" t="n">
+        <v>65500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>62900</v>
+      </c>
+      <c r="N9" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="O9" t="n">
+        <v>56007827150</v>
+      </c>
+      <c r="P9" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R9" t="n">
+        <v>162000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>자사주 매입 및 소각 관련 공시와 함께 수주 공시가 발표되어 신고가 도전 기대감이 있으며, 체질 변화에 대한 긍정적인 평가가 존재한다.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['자사주 소각', '수주 공시', '신고가']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16020</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-2.97%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>102</v>
+      </c>
+      <c r="H10" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>16510</v>
+      </c>
+      <c r="K10" t="n">
+        <v>16380</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16440</v>
+      </c>
+      <c r="M10" t="n">
+        <v>15940</v>
+      </c>
+      <c r="N10" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9484737470</v>
+      </c>
+      <c r="P10" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>15940</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-186000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>조선주 전반의 하락 추세 속에서 실적 발표 및 주주환원 정책 발표에 대한 불확실성이 존재하며, 유가 상승에도 불구하고 주가 반등이 제한적인 상황이다.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['조선주', '실적 발표', '주주환원']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>멜콘</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>18600</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-3.18%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>69</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>65</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>19210</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19010</v>
+      </c>
+      <c r="L11" t="n">
+        <v>19840</v>
+      </c>
+      <c r="M11" t="n">
+        <v>18440</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O11" t="n">
+        <v>52451959855</v>
+      </c>
+      <c r="P11" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>11550</v>
+      </c>
+      <c r="R11" t="n">
+        <v>53000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>반도체 섹터 전반의 하락 추세와 함께 주가 폭락에 대한 우려가 제기되고 있으며, 일부에서는 허매수 논란과 함께 고점 신호라는 분석도 존재한다.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['반도체', '폭락', '허매수']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12950</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-9.25%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G12" t="n">
+        <v>208</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12800</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O12" t="n">
+        <v>30261032625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R12" t="n">
+        <v>31000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>체코 원전 건설 시공 계약 최종 불발 소식이 주가 하락 요인으로 작용했으며, 공매도와 목표가 하향 조정에 대한 우려가 존재한다.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['체코 원전', '시공 계약', '공매도']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>20</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20261029_09.xlsx
+++ b/data/trending_integrated_20261029_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8610</v>
+        <v>9660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.57%</t>
+          <t>'+20.90%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.04</v>
+        <v>-0.67</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.42</v>
+        <v>17.97</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7450</v>
+        <v>7990</v>
       </c>
       <c r="K2" t="n">
-        <v>7470</v>
+        <v>8270</v>
       </c>
       <c r="L2" t="n">
-        <v>9680</v>
+        <v>10380</v>
       </c>
       <c r="M2" t="n">
-        <v>7360</v>
+        <v>7990</v>
       </c>
       <c r="N2" t="n">
-        <v>1.46</v>
+        <v>18.64</v>
       </c>
       <c r="O2" t="n">
-        <v>62461511285</v>
+        <v>82637435595</v>
       </c>
       <c r="P2" t="n">
-        <v>10300</v>
+        <v>22450</v>
       </c>
       <c r="Q2" t="n">
-        <v>952</v>
+        <v>1760</v>
       </c>
       <c r="R2" t="n">
-        <v>144000</v>
+        <v>78000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광주 반도체 공장 관련 뉴스와 함께 프로그램 매집 정황이 포착되며 주가 상승에 대한 기대감이 나타나고 있으나, 일부에서는 주가 조작에 대한 우려도 제기된다.</t>
+          <t>광통신 섹터의 강세와 미국 시장 상승에 따른 기대감. 다만, 차트상 하락 전환 가능성도 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광주 반도체', '프로그램 매집', '주가 조작']</t>
+          <t>['광통신', '차트', '미국 시장']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15910</v>
+        <v>8380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.21%</t>
+          <t>'+12.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.46</v>
+        <v>-1.04</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>428</v>
+        <v>74</v>
       </c>
       <c r="H3" t="n">
-        <v>3.33</v>
+        <v>0.42</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14980</v>
+        <v>7450</v>
       </c>
       <c r="K3" t="n">
-        <v>15120</v>
+        <v>7470</v>
       </c>
       <c r="L3" t="n">
-        <v>15950</v>
+        <v>9680</v>
       </c>
       <c r="M3" t="n">
-        <v>14650</v>
+        <v>7360</v>
       </c>
       <c r="N3" t="n">
-        <v>2.87</v>
+        <v>1.46</v>
       </c>
       <c r="O3" t="n">
-        <v>66051352465</v>
+        <v>71462709530</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>10300</v>
       </c>
       <c r="Q3" t="n">
-        <v>1819</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>-102000</v>
+        <v>144000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국장 및 광통신 섹터의 강세와 루멘텀 인수 기대감으로 주가 급등 가능성이 제기되고 있으며, 연말 3만 원 돌파 전망과 함께 계약 공시 기대감이 존재한다.</t>
+          <t>반도체 및 광주 반도체 관련 호재와 모건의 대량 매수 언급. 다만, 주가 조작 및 나락에 대한 경고도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀 인수', '계약 공시']</t>
+          <t>['반도체', '광주', '모건']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1567000</v>
+        <v>1563000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.38%</t>
+          <t>'+5.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G4" t="n">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="H4" t="n">
         <v>48.66</v>
@@ -785,7 +785,7 @@
         <v>1511000</v>
       </c>
       <c r="L4" t="n">
-        <v>1576000</v>
+        <v>1577000</v>
       </c>
       <c r="M4" t="n">
         <v>1501000</v>
@@ -794,7 +794,7 @@
         <v>48.61</v>
       </c>
       <c r="O4" t="n">
-        <v>1365453789500</v>
+        <v>1613589744500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SK하이닉스의 향후 주가 상승 전망이 강하게 제기되고 있으며, 자사주 매입 발표에 대한 기대감이 존재한다.</t>
+          <t>연이은 상승 추세와 주주환원 정책에 대한 긍정적 평가. 200만원 돌파 기대감 및 외국인 매수세 유입.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '자사주 매입', '주가 전망']</t>
+          <t>['주주환원', '외국인', '상승 추세']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4420</v>
+        <v>15270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.36%</t>
+          <t>'+1.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>118</v>
+        <v>476</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>3.33</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4195</v>
+        <v>14980</v>
       </c>
       <c r="K5" t="n">
-        <v>4280</v>
+        <v>15120</v>
       </c>
       <c r="L5" t="n">
-        <v>4480</v>
+        <v>15950</v>
       </c>
       <c r="M5" t="n">
-        <v>4100</v>
+        <v>14650</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>101146534737</v>
+        <v>83446672095</v>
       </c>
       <c r="P5" t="n">
-        <v>8100</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>592</v>
+        <v>1819</v>
       </c>
       <c r="R5" t="n">
-        <v>238000</v>
+        <v>-102000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>글로벌 광통신 섹터의 강세와 루멘텀의 폭등 소식에 힘입어 주가 상승 기대감이 고조되고 있으며, 5G 상용화 및 글로벌 기업 공급 시작과 관련된 긍정적인 뉴스가 존재한다.</t>
+          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 삼성전자의 투자 및 연말 3만 돌파 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '5G 상용화']</t>
+          <t>['광통신', '루멘텀', '삼성전자']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>551000</v>
+        <v>4260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.18%</t>
+          <t>'+1.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>539</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
-        <v>24.78</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>534000</v>
+        <v>4195</v>
       </c>
       <c r="K6" t="n">
-        <v>546000</v>
+        <v>4280</v>
       </c>
       <c r="L6" t="n">
-        <v>563000</v>
+        <v>4480</v>
       </c>
       <c r="M6" t="n">
-        <v>524000</v>
+        <v>4100</v>
       </c>
       <c r="N6" t="n">
-        <v>24.86</v>
+        <v>1.2</v>
       </c>
       <c r="O6" t="n">
-        <v>217950208500</v>
+        <v>113446486410</v>
       </c>
       <c r="P6" t="n">
-        <v>723000</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>259000</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>12000</v>
+        <v>238000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>컨퍼런스 콜에서 발표된 26년 3분기 영업이익이 컨센서스를 상회했으며, 실적 호조에 따른 주가 상승 기대감이 존재한다.</t>
+          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 다만, '개잡주'라는 부정적 언급도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['컨퍼런스 콜', '실적', '어닝 서프라이즈']</t>
+          <t>['광통신', '루멘텀', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>245750</v>
+        <v>542000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.55%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>155</v>
       </c>
       <c r="F7" t="n">
-        <v>463</v>
+        <v>93</v>
       </c>
       <c r="G7" t="n">
-        <v>1601</v>
+        <v>648</v>
       </c>
       <c r="H7" t="n">
-        <v>46.19</v>
+        <v>24.78</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>242000</v>
+        <v>534000</v>
       </c>
       <c r="K7" t="n">
-        <v>241000</v>
+        <v>546000</v>
       </c>
       <c r="L7" t="n">
-        <v>247500</v>
+        <v>563000</v>
       </c>
       <c r="M7" t="n">
-        <v>239000</v>
+        <v>524000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.15</v>
+        <v>24.86</v>
       </c>
       <c r="O7" t="n">
-        <v>898744423500</v>
+        <v>242069148500</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>723000</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>259000</v>
       </c>
       <c r="R7" t="n">
-        <v>258000</v>
+        <v>12000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>컨퍼런스 콜에서의 주주환원 정책 발표 기대감과 성과급 관련 논란이 혼재되어 있으며, 외인 매수세와 기관 매도세가 엇갈리고 있다.</t>
+          <t>컨퍼런스콜을 앞두고 3분기 실적 호조 및 전고체 관련주 급등세 반영. 컨센서스 상회한 영업이익 및 금리 동결, 유가 하락 등 긍정적 요인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['컨퍼런스 콜', '주주환원', '성과급']</t>
+          <t>['컨퍼런스콜', '실적', '전고체']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14460</v>
+        <v>244500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+1.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>472</v>
       </c>
       <c r="G8" t="n">
-        <v>182</v>
+        <v>1612</v>
       </c>
       <c r="H8" t="n">
-        <v>8.050000000000001</v>
+        <v>46.19</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14390</v>
+        <v>242000</v>
       </c>
       <c r="K8" t="n">
-        <v>15450</v>
+        <v>241000</v>
       </c>
       <c r="L8" t="n">
-        <v>16290</v>
+        <v>247500</v>
       </c>
       <c r="M8" t="n">
-        <v>14430</v>
+        <v>239000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.109999999999999</v>
+        <v>46.15</v>
       </c>
       <c r="O8" t="n">
-        <v>28631924740</v>
+        <v>1092326369500</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-168000</v>
+        <v>258000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 급등 및 ESMO 2026 스코프에 대한 기대감. 3분기 실적 발표까지 보유 전망.</t>
+          <t>주주환원 정책 발표 기대감 속에서 외국인 매수세 유입. 다만, 노조 이슈와 컨퍼런스콜 타이밍에 대한 부정적 시각도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 AI', 'ESMO 2026', '실적 발표']</t>
+          <t>['주주환원', '컨퍼런스콜', '외국인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62900</v>
+        <v>14400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.54</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="H9" t="n">
-        <v>41.55</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>64200</v>
+        <v>14390</v>
       </c>
       <c r="K9" t="n">
-        <v>64200</v>
+        <v>15450</v>
       </c>
       <c r="L9" t="n">
-        <v>65500</v>
+        <v>16290</v>
       </c>
       <c r="M9" t="n">
-        <v>62900</v>
+        <v>14340</v>
       </c>
       <c r="N9" t="n">
-        <v>41.01</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>56007827150</v>
+        <v>31009653895</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>162000</v>
+        <v>-168000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 관련 공시와 함께 수주 공시가 발표되어 신고가 도전 기대감이 있으며, 체질 변화에 대한 긍정적인 평가가 존재한다.</t>
+          <t>미국 의료 AI 및 템퍼스 AI 급등에 따른 시초 상승 기대. ESMO 2026 스코프 및 3분기 실적 발표 전까지 보유 전략.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주 소각', '수주 공시', '신고가']</t>
+          <t>['의료AI', '템퍼스AI', 'ESMO']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16020</v>
+        <v>63200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>28.07</v>
+        <v>41.55</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16510</v>
+        <v>64200</v>
       </c>
       <c r="K10" t="n">
-        <v>16380</v>
+        <v>64200</v>
       </c>
       <c r="L10" t="n">
-        <v>16440</v>
+        <v>65500</v>
       </c>
       <c r="M10" t="n">
-        <v>15940</v>
+        <v>62500</v>
       </c>
       <c r="N10" t="n">
-        <v>28.03</v>
+        <v>41.01</v>
       </c>
       <c r="O10" t="n">
-        <v>9484737470</v>
+        <v>65528389050</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>15940</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-186000</v>
+        <v>162000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락 추세 속에서 실적 발표 및 주주환원 정책 발표에 대한 불확실성이 존재하며, 유가 상승에도 불구하고 주가 반등이 제한적인 상황이다.</t>
+          <t>자사주 매입 및 소각 관련 긍정적 언급과 함께 수주 공시 확인. 체질 변화에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선주', '실적 발표', '주주환원']</t>
+          <t>['자사주', '수주 공시', '체질 변화']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18600</v>
+        <v>15840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="H11" t="n">
-        <v>0.65</v>
+        <v>28.07</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19210</v>
+        <v>16510</v>
       </c>
       <c r="K11" t="n">
-        <v>19010</v>
+        <v>16380</v>
       </c>
       <c r="L11" t="n">
-        <v>19840</v>
+        <v>16440</v>
       </c>
       <c r="M11" t="n">
-        <v>18440</v>
+        <v>15810</v>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>28.03</v>
       </c>
       <c r="O11" t="n">
-        <v>52451959855</v>
+        <v>14022075750</v>
       </c>
       <c r="P11" t="n">
-        <v>28800</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>11550</v>
+        <v>15810</v>
       </c>
       <c r="R11" t="n">
-        <v>53000</v>
+        <v>-186000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 섹터 전반의 하락 추세와 함께 주가 폭락에 대한 우려가 제기되고 있으며, 일부에서는 허매수 논란과 함께 고점 신호라는 분석도 존재한다.</t>
+          <t>연속적인 신저점 갱신 및 부정적인 전망. 실적 부진과 향후 전망에 대한 우려 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '폭락', '허매수']</t>
+          <t>['신저점', '실적 부진', '향후 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12950</v>
+        <v>18250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-9.25%</t>
+          <t>'-5.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.23</v>
+        <v>-0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="H12" t="n">
-        <v>9.6</v>
+        <v>0.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14270</v>
+        <v>19210</v>
       </c>
       <c r="K12" t="n">
-        <v>14180</v>
+        <v>19010</v>
       </c>
       <c r="L12" t="n">
-        <v>14180</v>
+        <v>19840</v>
       </c>
       <c r="M12" t="n">
-        <v>12800</v>
+        <v>18120</v>
       </c>
       <c r="N12" t="n">
-        <v>9.83</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
-        <v>30261032625</v>
+        <v>58715032820</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>11550</v>
       </c>
       <c r="R12" t="n">
-        <v>31000</v>
+        <v>53000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>체코 원전 건설 시공 계약 최종 불발 소식이 주가 하락 요인으로 작용했으며, 공매도와 목표가 하향 조정에 대한 우려가 존재한다.</t>
+          <t>반도체 대폭락과 보호예수 물량 출회에 따른 하락세 전망. 전일 거래량 증가와 마이크론 급락 등 요인 고려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,18 +1555,202 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공 계약', '공매도']</t>
+          <t>['반도체', '보호예수', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>55400</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-9.77%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>110</v>
+      </c>
+      <c r="G13" t="n">
+        <v>382</v>
+      </c>
+      <c r="H13" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>61400</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60600</v>
+      </c>
+      <c r="L13" t="n">
+        <v>60800</v>
+      </c>
+      <c r="M13" t="n">
+        <v>55200</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="O13" t="n">
+        <v>56876965300</v>
+      </c>
+      <c r="P13" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>55200</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-33000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>체코 원전 건설 시공 계약 최종 불발 및 실적 쇼크 소식에 따른 주가 하락 우려. '개잡주'라는 부정적 평가 다수.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['체코 원전', '시공 계약', '실적 쇼크']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>11900</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-16.61%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>141</v>
+      </c>
+      <c r="F14" t="n">
+        <v>94</v>
+      </c>
+      <c r="G14" t="n">
+        <v>296</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11540</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O14" t="n">
+        <v>75794651870</v>
+      </c>
+      <c r="P14" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R14" t="n">
+        <v>31000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>체코 원전 건설 시공 계약 불발 및 목표가 하향 소식에 따른 주가 하락 우려. 정치적 이슈도 언급.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['체코 원전', '시공 계약', '목표가 하향']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>20</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20261029_09.xlsx
+++ b/data/trending_integrated_20261029_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9660</v>
+        <v>9580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.90%</t>
+          <t>'+19.90%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.67</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
         <v>17.97</v>
@@ -610,7 +610,7 @@
         <v>18.64</v>
       </c>
       <c r="O2" t="n">
-        <v>82637435595</v>
+        <v>89355867530</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -619,23 +619,23 @@
         <v>1760</v>
       </c>
       <c r="R2" t="n">
-        <v>78000</v>
+        <v>135000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 미국 시장 상승에 따른 기대감. 다만, 차트상 하락 전환 가능성도 언급.</t>
+          <t>미국 광통신 기업 루멘텀의 급등 소식과 서울반도체의 희토류 없는 LED 개발 언급. 다만, 프로그램 매도 전환 및 차익 실현 움직임 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '차트', '미국 시장']</t>
+          <t>['광통신', 'LED', '차트']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8380</v>
+        <v>8110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.48%</t>
+          <t>'+8.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.04</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>0.42</v>
@@ -702,7 +702,7 @@
         <v>1.46</v>
       </c>
       <c r="O3" t="n">
-        <v>71462709530</v>
+        <v>75096041535</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -711,23 +711,23 @@
         <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>144000</v>
+        <v>506000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>반도체 및 광주 반도체 관련 호재와 모건의 대량 매수 언급. 다만, 주가 조작 및 나락에 대한 경고도 존재.</t>
+          <t>하이닉스 물량 완판 및 광주 반도체 사업 속도전 관련 언급. 주가 상승 및 하락에 대한 상반된 전망. 특정 주체(주포, 모건)의 움직임 주목.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '광주', '모건']</t>
+          <t>['반도체', '광주', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1563000</v>
+        <v>37850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.11%</t>
+          <t>'+8.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>459</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>1723</v>
+        <v>108</v>
       </c>
       <c r="H4" t="n">
-        <v>48.66</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1487000</v>
+        <v>34800</v>
       </c>
       <c r="K4" t="n">
-        <v>1511000</v>
+        <v>36600</v>
       </c>
       <c r="L4" t="n">
-        <v>1577000</v>
+        <v>40200</v>
       </c>
       <c r="M4" t="n">
-        <v>1501000</v>
+        <v>36200</v>
       </c>
       <c r="N4" t="n">
-        <v>48.61</v>
+        <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>1613589744500</v>
+        <v>68711535500</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>126600</v>
       </c>
       <c r="Q4" t="n">
-        <v>501000</v>
+        <v>15260</v>
       </c>
       <c r="R4" t="n">
-        <v>146000</v>
+        <v>52000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>연이은 상승 추세와 주주환원 정책에 대한 긍정적 평가. 200만원 돌파 기대감 및 외국인 매수세 유입.</t>
+          <t>루멘텀의 급등 소식과 함께 RF머트리얼즈가 수혜주로 언급되며 3분기 실적에 대한 긍정적 전망이 부각됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주주환원', '외국인', '상승 추세']</t>
+          <t>['루멘텀', 'RF머트리얼즈', '실적 기대']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>327260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15270</v>
+        <v>1560000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+4.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>479</v>
       </c>
       <c r="G5" t="n">
-        <v>476</v>
+        <v>1716</v>
       </c>
       <c r="H5" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14980</v>
+        <v>1487000</v>
       </c>
       <c r="K5" t="n">
-        <v>15120</v>
+        <v>1511000</v>
       </c>
       <c r="L5" t="n">
-        <v>15950</v>
+        <v>1587000</v>
       </c>
       <c r="M5" t="n">
-        <v>14650</v>
+        <v>1501000</v>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>48.61</v>
       </c>
       <c r="O5" t="n">
-        <v>83446672095</v>
+        <v>1846145712000</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1819</v>
+        <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>-102000</v>
+        <v>281000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 삼성전자의 투자 및 연말 3만 돌파 전망.</t>
+          <t>SK하이닉스의 실적 발표 후 주가 상승 기대감. 200만원 돌파 전망과 함께 자사주 매입 및 주주환원 정책에 대한 긍정적 평가. 반도체 섹터 대장주로서의 입지 부각.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '삼성전자']</t>
+          <t>['실적 발표', '주주환원', '반도체']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4260</v>
+        <v>245000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.55%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>474</v>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>1648</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>46.19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4195</v>
+        <v>242000</v>
       </c>
       <c r="K6" t="n">
-        <v>4280</v>
+        <v>241000</v>
       </c>
       <c r="L6" t="n">
-        <v>4480</v>
+        <v>249000</v>
       </c>
       <c r="M6" t="n">
-        <v>4100</v>
+        <v>239000</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>46.15</v>
       </c>
       <c r="O6" t="n">
-        <v>113446486410</v>
+        <v>1325018424500</v>
       </c>
       <c r="P6" t="n">
-        <v>8100</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>592</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>238000</v>
+        <v>166000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-505000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 다만, '개잡주'라는 부정적 언급도 존재.</t>
+          <t>주주환원 정책 발표 및 실적 발표 기대감. 노조 관련 이슈와 함께 프리장에서의 주가 움직임 주목. 전반적으로 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '기대감']</t>
+          <t>['주주환원', '실적 발표', '컨퍼런스콜']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>542000</v>
+        <v>15120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+0.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="E7" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>648</v>
+        <v>496</v>
       </c>
       <c r="H7" t="n">
-        <v>24.78</v>
+        <v>3.33</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>534000</v>
+        <v>14980</v>
       </c>
       <c r="K7" t="n">
-        <v>546000</v>
+        <v>15120</v>
       </c>
       <c r="L7" t="n">
-        <v>563000</v>
+        <v>15950</v>
       </c>
       <c r="M7" t="n">
-        <v>524000</v>
+        <v>14650</v>
       </c>
       <c r="N7" t="n">
-        <v>24.86</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>242069148500</v>
+        <v>91438980405</v>
       </c>
       <c r="P7" t="n">
-        <v>723000</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>259000</v>
+        <v>1819</v>
       </c>
       <c r="R7" t="n">
-        <v>12000</v>
+        <v>-213000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>컨퍼런스콜을 앞두고 3분기 실적 호조 및 전고체 관련주 급등세 반영. 컨센서스 상회한 영업이익 및 금리 동결, 유가 하락 등 긍정적 요인.</t>
+          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 삼성전자의 투자 및 연말 3만 돌파 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '실적', '전고체']</t>
+          <t>['광통신', '루멘텀', '삼성전자']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>244500</v>
+        <v>534000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.03%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
-        <v>472</v>
+        <v>103</v>
       </c>
       <c r="G8" t="n">
-        <v>1612</v>
+        <v>685</v>
       </c>
       <c r="H8" t="n">
-        <v>46.19</v>
+        <v>24.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>242000</v>
+        <v>534000</v>
       </c>
       <c r="K8" t="n">
-        <v>241000</v>
+        <v>546000</v>
       </c>
       <c r="L8" t="n">
-        <v>247500</v>
+        <v>563000</v>
       </c>
       <c r="M8" t="n">
-        <v>239000</v>
+        <v>524000</v>
       </c>
       <c r="N8" t="n">
-        <v>46.15</v>
+        <v>24.86</v>
       </c>
       <c r="O8" t="n">
-        <v>1092326369500</v>
+        <v>257354729500</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>723000</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>259000</v>
       </c>
       <c r="R8" t="n">
-        <v>258000</v>
+        <v>6000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주주환원 정책 발표 기대감 속에서 외국인 매수세 유입. 다만, 노조 이슈와 컨퍼런스콜 타이밍에 대한 부정적 시각도 존재.</t>
+          <t>컨퍼런스콜을 앞두고 3분기 실적 호조 및 전고체 관련주 급등세 반영. 컨센서스 상회한 영업이익 및 금리 동결, 유가 하락 등 긍정적 요인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', '컨퍼런스콜', '외국인']</t>
+          <t>['컨퍼런스콜', '실적', '전고체']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14400</v>
+        <v>14300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="H9" t="n">
         <v>8.050000000000001</v>
@@ -1248,13 +1248,13 @@
         <v>16290</v>
       </c>
       <c r="M9" t="n">
-        <v>14340</v>
+        <v>14040</v>
       </c>
       <c r="N9" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>31009653895</v>
+        <v>33849185515</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1263,23 +1263,23 @@
         <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-168000</v>
+        <v>-192000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 의료 AI 및 템퍼스 AI 급등에 따른 시초 상승 기대. ESMO 2026 스코프 및 3분기 실적 발표 전까지 보유 전략.</t>
+          <t>의료 AI 분야의 성장 기대감과 함께 차트상의 긍정적 신호가 관찰되나, 단기적인 변동성에 대한 우려도 존재함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료AI', '템퍼스AI', 'ESMO']</t>
+          <t>['의료 AI', '차트 분석', '단기 변동성']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63200</v>
+        <v>63400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="H10" t="n">
         <v>41.55</v>
@@ -1346,7 +1346,7 @@
         <v>41.01</v>
       </c>
       <c r="O10" t="n">
-        <v>65528389050</v>
+        <v>73555517150</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1355,23 +1355,23 @@
         <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>162000</v>
+        <v>271000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 관련 긍정적 언급과 함께 수주 공시 확인. 체질 변화에 대한 기대감 표출.</t>
+          <t>자사주 매입 및 소각 관련 언급과 함께 수주 공시 확인. 신고가 도전 및 66 돌파 기대감. 공매도 세력에 대한 방어 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주', '수주 공시', '체질 변화']</t>
+          <t>['자사주', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15840</v>
+        <v>4130</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-1.55%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H11" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K11" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L11" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M11" t="n">
-        <v>15810</v>
+        <v>4100</v>
       </c>
       <c r="N11" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>14022075750</v>
+        <v>121731269682</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>15810</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-186000</v>
+        <v>-347000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>연속적인 신저점 갱신 및 부정적인 전망. 실적 부진과 향후 전망에 대한 우려 표출.</t>
+          <t>미국 광통신 기업 루멘텀의 급등 소식과 연관된 광통신 섹터의 강세. 5G 상용화 성공 및 글로벌 기업 공급 시작 뉴스 언급. 개인 투자자 매물 소화 후 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신저점', '실적 부진', '향후 전망']</t>
+          <t>['광통신', '루멘텀', '5G']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18250</v>
+        <v>15800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.00%</t>
+          <t>'-4.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H12" t="n">
-        <v>0.65</v>
+        <v>28.07</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19210</v>
+        <v>16510</v>
       </c>
       <c r="K12" t="n">
-        <v>19010</v>
+        <v>16380</v>
       </c>
       <c r="L12" t="n">
-        <v>19840</v>
+        <v>16440</v>
       </c>
       <c r="M12" t="n">
-        <v>18120</v>
+        <v>15800</v>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>28.03</v>
       </c>
       <c r="O12" t="n">
-        <v>58715032820</v>
+        <v>17509379075</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>11550</v>
+        <v>15800</v>
       </c>
       <c r="R12" t="n">
-        <v>53000</v>
+        <v>-348000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 대폭락과 보호예수 물량 출회에 따른 하락세 전망. 전일 거래량 증가와 마이크론 급락 등 요인 고려.</t>
+          <t>연이은 신저점 갱신 및 주가 부진에 대한 불만 토로. 금리 동결, 유가 상승에도 불구하고 조선주 반등 기대감이 낮음. 중국에 대한 경쟁력 약화 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '보호예수', '거래량']</t>
+          <t>['신저점', '조선주', '주가 부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55400</v>
+        <v>18000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.77%</t>
+          <t>'-6.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>-0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>382</v>
+        <v>72</v>
       </c>
       <c r="H13" t="n">
-        <v>22.34</v>
+        <v>0.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>61400</v>
+        <v>19210</v>
       </c>
       <c r="K13" t="n">
-        <v>60600</v>
+        <v>19010</v>
       </c>
       <c r="L13" t="n">
-        <v>60800</v>
+        <v>19840</v>
       </c>
       <c r="M13" t="n">
-        <v>55200</v>
+        <v>17800</v>
       </c>
       <c r="N13" t="n">
-        <v>22.32</v>
+        <v>1.11</v>
       </c>
       <c r="O13" t="n">
-        <v>56876965300</v>
+        <v>65167987500</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>55200</v>
+        <v>11550</v>
       </c>
       <c r="R13" t="n">
-        <v>-33000</v>
+        <v>7000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>체코 원전 건설 시공 계약 최종 불발 및 실적 쇼크 소식에 따른 주가 하락 우려. '개잡주'라는 부정적 평가 다수.</t>
+          <t>보호 예수 물량 출회 및 반도체 섹터 대폭락 우려로 인한 주가 하락. 마이크론의 하락 마감 및 전반적인 하락세 지속. 고점이라는 인식 확산.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공 계약', '실적 쇼크']</t>
+          <t>['보호 예수', '반도체 대폭락', '하락 vi']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11900</v>
+        <v>53700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-16.61%</t>
+          <t>'-12.54%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.23</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="G14" t="n">
-        <v>296</v>
+        <v>656</v>
       </c>
       <c r="H14" t="n">
-        <v>9.6</v>
+        <v>22.34</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,58 +1699,150 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14270</v>
+        <v>61400</v>
       </c>
       <c r="K14" t="n">
-        <v>14180</v>
+        <v>60600</v>
       </c>
       <c r="L14" t="n">
-        <v>14180</v>
+        <v>60800</v>
       </c>
       <c r="M14" t="n">
-        <v>11540</v>
+        <v>53700</v>
       </c>
       <c r="N14" t="n">
-        <v>9.83</v>
+        <v>22.32</v>
       </c>
       <c r="O14" t="n">
-        <v>75794651870</v>
+        <v>106776215750</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>53700</v>
       </c>
       <c r="R14" t="n">
-        <v>31000</v>
+        <v>-351000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-92000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>체코 원전 건설 시공 계약 불발 및 목표가 하향 소식에 따른 주가 하락 우려. 정치적 이슈도 언급.</t>
+          <t>체코 원전 사업 계약 최종 불발 소식으로 인한 주가 하락. 대우건설과의 계약 파기 이슈가 부각되나, 기자재 관련 영향은 제한적이라는 분석도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공 계약', '목표가 하향']</t>
+          <t>['체코 원전', '계약 불발', '두산에너빌리티']</t>
         </is>
       </c>
       <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11460</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-19.69%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>195</v>
+      </c>
+      <c r="F15" t="n">
+        <v>125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>416</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11460</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>105749522105</v>
+      </c>
+      <c r="P15" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-653000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>체코 원전 사업 관련 계약 불발 및 협상 종료 소식. 정치적 이슈와 공매도 관련 언급 다수. 주가 하락 지속.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['체코 원전', '공매도', '대우건설']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>20</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>047040</t>
         </is>
